--- a/data/export/2026-10-29-182路.xlsx
+++ b/data/export/2026-10-29-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A32298D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>07:25</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       <c r="T9" s="2" t="inlineStr"/>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1492,7 +1492,673 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-182路.xlsx
+++ b/data/export/2026-10-29-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1603,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1714,7 +1714,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1825,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2055,22 +2055,22 @@
       <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       <c r="T15" s="2" t="inlineStr"/>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2158,7 +2158,895 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-182路.xlsx
+++ b/data/export/2026-10-29-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2943,22 +2943,22 @@
       <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>沪A32298D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2991,12 +2991,12 @@
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3010,7 +3010,7 @@
       <c r="T23" s="2" t="inlineStr"/>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -3045,6 +3045,561 @@
       </c>
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
         <is>
           <t>—/13</t>
         </is>

--- a/data/export/2026-10-29-182路.xlsx
+++ b/data/export/2026-10-29-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3498,22 +3498,22 @@
       <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       <c r="T28" s="2" t="inlineStr"/>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3600,6 +3600,339 @@
       </c>
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
         <is>
           <t>—/13</t>
         </is>

--- a/data/export/2026-10-29-182路.xlsx
+++ b/data/export/2026-10-29-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3831,22 +3831,22 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -3933,6 +3933,561 @@
       </c>
       <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
         <is>
           <t>—/13</t>
         </is>

--- a/data/export/2026-10-29-182路.xlsx
+++ b/data/export/2026-10-29-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4493,6 +4493,561 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-29-182路.xlsx
+++ b/data/export/2026-10-29-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC41"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5048,6 +5048,672 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-29-182路.xlsx
+++ b/data/export/2026-10-29-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5714,6 +5714,450 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-29-182路.xlsx
+++ b/data/export/2026-10-29-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6158,6 +6158,561 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-29-182路.xlsx
+++ b/data/export/2026-10-29-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,13 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -776,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -887,7 +891,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -998,7 +1002,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1041,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1109,7 +1113,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1148,7 +1152,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1220,7 +1224,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1259,7 +1263,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1331,7 +1335,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1375,13 +1379,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1450,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1481,7 +1489,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1553,7 +1561,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1597,13 +1605,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1676,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1703,18 +1715,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2013,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2108,7 +2124,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2152,13 +2168,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2239,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2330,7 +2350,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2369,7 +2389,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2441,7 +2461,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2552,7 +2572,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2591,7 +2611,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2663,7 +2683,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2702,7 +2722,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2774,7 +2794,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2818,13 +2838,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2909,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2924,7 +2948,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -2996,7 +3020,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3040,13 +3064,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3135,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3146,18 +3174,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3472,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3551,7 +3583,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3595,13 +3627,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3698,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3701,7 +3737,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3773,7 +3809,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3884,7 +3920,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3995,7 +4031,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4034,7 +4070,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4106,7 +4142,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4150,13 +4186,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB33" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4257,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4256,7 +4296,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4328,7 +4368,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4367,18 +4407,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4594,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4772,7 +4816,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4811,7 +4855,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -4883,7 +4927,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4994,7 +5038,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5033,7 +5077,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5105,7 +5149,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5144,7 +5188,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5216,7 +5260,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5260,13 +5304,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5486,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5482,13 +5530,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5712,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5771,7 +5823,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5849,32 +5901,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5882,7 +5938,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -5906,17 +5962,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -5926,13 +5982,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB49" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -5960,32 +6020,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:52</t>
@@ -5993,7 +6057,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6017,17 +6081,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6037,13 +6101,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB50" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -6071,32 +6139,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -6104,7 +6176,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6128,33 +6200,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB51" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -6182,32 +6258,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6215,7 +6295,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6239,17 +6319,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6259,13 +6339,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB52" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6410,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6365,7 +6449,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6437,7 +6521,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6548,7 +6632,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6659,7 +6743,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6703,11 +6787,574 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB56" s="2" t="inlineStr"/>
-      <c r="AC56" s="2" t="inlineStr">
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>2/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
         <is>
           <t>—/13</t>
         </is>

--- a/data/export/2026-10-29-182路.xlsx
+++ b/data/export/2026-10-29-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,18 +819,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -891,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -935,13 +939,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1041,7 +1049,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1113,7 +1121,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1152,18 +1160,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1236,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1268,13 +1280,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1351,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1379,17 +1395,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1561,7 +1577,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1600,7 +1616,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1615,7 +1631,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1692,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1730,7 +1746,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1830,7 +1846,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1902,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1941,7 +1957,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2013,7 +2029,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2052,18 +2068,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2144,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2163,7 +2183,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2173,12 +2193,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2283,13 +2303,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2374,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2389,7 +2413,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2572,7 +2596,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2611,18 +2635,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2711,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2727,13 +2755,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2826,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2838,17 +2870,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2941,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3020,7 +3052,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3059,7 +3091,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3074,7 +3106,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3167,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3189,7 +3221,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3282,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3289,7 +3321,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3361,7 +3393,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3400,7 +3432,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3472,7 +3504,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3511,18 +3543,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3619,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3622,7 +3658,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3632,12 +3668,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3734,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3737,7 +3773,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3809,7 +3845,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3853,13 +3889,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB30" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4071,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4070,18 +4110,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4186,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4186,17 +4230,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4301,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4368,7 +4412,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4422,7 +4466,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4483,7 +4527,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4522,7 +4566,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4594,7 +4638,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4633,18 +4677,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB37" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4753,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4744,7 +4792,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4816,7 +4864,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4855,7 +4903,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5038,7 +5086,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5077,18 +5125,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB41" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5201,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5260,7 +5312,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5299,7 +5351,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5314,7 +5366,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5427,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5414,7 +5466,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5486,7 +5538,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5525,7 +5577,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5535,12 +5587,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5653,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5640,7 +5692,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5712,7 +5764,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5756,13 +5808,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5994,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -5982,17 +6038,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -6057,7 +6113,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6096,7 +6152,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6111,7 +6167,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6232,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6230,7 +6286,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -6268,24 +6324,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6295,7 +6351,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6334,7 +6390,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6344,12 +6400,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -6377,32 +6433,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -6410,7 +6470,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6434,17 +6494,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6454,13 +6514,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB53" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -6488,32 +6552,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6521,7 +6589,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6545,17 +6613,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6565,13 +6633,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB54" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -6599,32 +6671,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6632,7 +6708,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6656,33 +6732,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB55" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -6710,32 +6790,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6743,7 +6827,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6767,17 +6851,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -6787,17 +6871,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -6825,32 +6909,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6858,7 +6946,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -6882,33 +6970,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -6969,7 +7061,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7023,7 +7115,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -7084,7 +7176,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7123,7 +7215,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7195,7 +7287,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7306,7 +7398,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7350,11 +7442,808 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>1/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr"/>
-      <c r="AC61" s="2" t="inlineStr">
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>7/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>2/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
         <is>
           <t>—/13</t>
         </is>

--- a/data/export/2026-10-29-182路.xlsx
+++ b/data/export/2026-10-29-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8027,22 +8027,22 @@
       <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8142,7 @@
       <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8209,41 +8209,156 @@
       <c r="T68" s="2" t="inlineStr"/>
       <c r="U68" s="2" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>2/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="V68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W68" s="2" t="inlineStr">
+      <c r="W69" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X68" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y68" s="2" t="inlineStr">
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z68" s="2" t="inlineStr">
+      <c r="Z69" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
+      <c r="AA69" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr"/>
-      <c r="AC68" s="2" t="inlineStr">
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
         <is>
           <t>—/13</t>
         </is>

--- a/data/export/2026-10-29-182路.xlsx
+++ b/data/export/2026-10-29-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC69"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1054,13 +1054,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1175,7 +1179,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1240,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1280,17 +1284,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1390,22 +1394,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1470,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1505,18 +1509,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1616,7 +1624,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1631,7 +1639,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1700,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1731,22 +1739,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1846,7 +1854,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1918,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,7 +2037,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2083,7 +2091,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2152,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2198,7 +2206,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2267,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2313,7 +2321,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2382,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2418,13 +2426,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2497,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2524,7 +2536,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2596,7 +2608,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2650,7 +2662,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2723,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2755,17 +2767,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2838,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2865,22 +2877,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2953,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2980,18 +2992,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3068,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3091,7 +3107,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3106,7 +3122,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3183,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3206,22 +3222,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3298,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3321,7 +3337,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3393,7 +3409,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3504,7 +3520,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3558,7 +3574,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3635,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3673,7 +3689,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3750,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3778,13 +3794,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3865,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3899,7 +3919,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3980,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3999,7 +4019,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4071,7 +4091,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4125,7 +4145,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4206,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4225,22 +4245,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4321,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4340,18 +4360,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4436,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4451,22 +4475,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4551,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4566,7 +4590,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4638,7 +4662,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4692,7 +4716,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4777,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4864,7 +4888,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4908,13 +4932,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4975,7 +5003,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5014,7 +5042,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5086,7 +5114,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5140,7 +5168,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5229,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5240,18 +5268,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5344,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5351,7 +5383,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5366,7 +5398,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5459,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5466,7 +5498,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5538,7 +5570,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5592,7 +5624,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5685,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5764,7 +5796,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5818,7 +5850,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5911,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5918,7 +5950,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -5994,7 +6026,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6033,22 +6065,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6145,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6152,7 +6184,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6167,7 +6199,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6264,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6271,22 +6303,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6383,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6405,7 +6437,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6502,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6514,17 +6546,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6621,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6643,7 +6675,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6740,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6762,7 +6794,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -6790,36 +6822,32 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6827,7 +6855,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6851,37 +6879,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6974,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7000,7 +7028,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -7028,32 +7056,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -7061,7 +7093,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7085,37 +7117,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -7143,32 +7175,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7176,7 +7212,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7200,17 +7236,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7220,13 +7256,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -7254,32 +7294,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -7287,7 +7331,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7311,33 +7355,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -7365,32 +7413,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -7398,7 +7450,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7422,17 +7474,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7442,17 +7494,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7565,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7552,7 +7604,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7624,7 +7676,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7663,7 +7715,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7678,7 +7730,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -7739,7 +7791,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7793,7 +7845,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7906,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -7908,7 +7960,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -7969,7 +8021,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8080,7 +8132,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8134,7 +8186,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -8195,7 +8247,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8249,7 +8301,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8362,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8354,13 +8406,699 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr"/>
-      <c r="AC69" s="2" t="inlineStr">
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
         <is>
           <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>6/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>7/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>2/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>9/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-182路.xlsx
+++ b/data/export/2026-10-29-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,22 +819,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -934,22 +934,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1054,17 +1054,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1164,22 +1164,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2076,22 +2076,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2306,22 +2306,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2426,17 +2426,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2536,18 +2536,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2612,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2647,22 +2651,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2727,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2772,12 +2776,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2842,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2892,7 +2896,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2957,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2992,7 +2996,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3007,7 +3011,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3072,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3112,17 +3116,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3187,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3237,7 +3241,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3302,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3409,7 +3413,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3448,7 +3452,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3520,7 +3524,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3559,22 +3563,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3639,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3674,7 +3678,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3689,7 +3693,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3754,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3794,17 +3798,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3869,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3904,22 +3908,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3984,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4019,18 +4023,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4099,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4130,22 +4138,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4214,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4260,7 +4268,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4329,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4360,7 +4368,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4375,7 +4383,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4444,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4490,7 +4498,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4559,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4662,7 +4670,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4701,22 +4709,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -4777,7 +4785,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4816,7 +4824,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4888,7 +4896,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4932,17 +4940,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5011,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5042,18 +5050,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB40" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5126,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5153,22 +5165,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5241,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5268,7 +5280,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5283,7 +5295,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5356,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5388,17 +5400,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5471,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5570,7 +5582,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5609,7 +5621,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5624,7 +5636,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5697,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5724,7 +5736,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5796,7 +5808,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5835,22 +5847,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -5911,7 +5923,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5950,18 +5962,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB48" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6042,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6080,7 +6096,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6161,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6189,17 +6205,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6280,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6318,7 +6334,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6399,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6422,7 +6438,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6437,7 +6453,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -6502,7 +6518,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6551,12 +6567,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -6621,7 +6637,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6660,22 +6676,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6756,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6779,22 +6795,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -6855,7 +6871,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6909,7 +6925,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6990,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7013,22 +7029,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7109,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7147,7 +7163,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7228,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7256,17 +7272,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7347,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7370,7 +7386,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7385,7 +7401,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -7423,24 +7439,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7450,7 +7466,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7499,12 +7515,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -7565,7 +7581,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7643,32 +7659,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:52</t>
@@ -7676,7 +7696,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7700,17 +7720,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7720,17 +7740,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -7758,32 +7778,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7791,7 +7815,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7815,37 +7839,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7930,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -7945,7 +7969,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -7960,7 +7984,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8045,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8060,7 +8084,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8099,32 +8123,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8132,7 +8160,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8156,37 +8184,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -8214,32 +8242,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8247,7 +8279,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8271,37 +8303,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -8329,32 +8361,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8362,7 +8398,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8386,17 +8422,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8406,17 +8442,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -8444,32 +8480,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -8477,7 +8517,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8501,33 +8541,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB70" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8632,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8627,7 +8671,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8642,7 +8686,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8747,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8814,7 +8858,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -8868,7 +8912,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -8929,7 +8973,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -8973,17 +9017,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -9044,7 +9088,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9098,7 +9142,808 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>1/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>2/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-182路.xlsx
+++ b/data/export/2026-10-29-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,22 +819,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1394,22 +1394,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1514,17 +1514,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1739,22 +1739,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1854,18 +1854,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2041,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2076,22 +2080,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2156,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2267,7 +2271,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2321,7 +2325,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2386,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2436,7 +2440,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2501,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2546,7 +2550,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2612,7 +2616,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2666,7 +2670,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2785,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2846,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2881,22 +2885,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2961,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3001,17 +3005,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3076,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3116,17 +3120,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3191,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3226,22 +3230,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3306,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3341,18 +3345,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3532,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3563,22 +3571,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3647,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3754,7 +3762,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3808,7 +3816,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3877,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3923,7 +3931,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3992,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4033,7 +4041,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4099,7 +4107,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4153,7 +4161,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4222,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4253,22 +4261,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4337,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4373,17 +4381,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4452,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4483,22 +4491,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4567,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4598,18 +4606,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB36" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4682,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4709,22 +4721,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4908,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4950,7 +4962,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5023,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5060,7 +5072,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5126,7 +5138,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5180,7 +5192,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5253,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5285,17 +5297,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5368,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5400,17 +5412,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5483,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5510,18 +5522,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5598,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5808,7 +5824,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5862,7 +5878,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -5923,7 +5939,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5972,7 +5988,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6042,7 +6058,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6081,22 +6097,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6177,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6205,17 +6221,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -6280,7 +6296,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6319,22 +6335,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -6399,7 +6415,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6572,7 +6588,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6653,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6691,7 +6707,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6772,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6795,22 +6811,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6887,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6910,22 +6926,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -6990,7 +7006,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7044,7 +7060,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7125,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7148,22 +7164,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -7228,7 +7244,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7282,7 +7298,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -7347,7 +7363,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7391,17 +7407,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -7520,7 +7536,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -7581,7 +7597,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7620,18 +7636,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB62" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -7696,7 +7716,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7740,17 +7760,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7835,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7854,22 +7874,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7950,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8160,7 +8180,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8214,7 +8234,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -8279,7 +8299,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8333,7 +8353,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -8383,12 +8403,12 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8398,7 +8418,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8452,7 +8472,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -8490,24 +8510,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8517,7 +8537,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8566,7 +8586,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8599,32 +8619,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -8632,7 +8656,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8656,17 +8680,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8676,17 +8700,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -8714,32 +8738,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -8747,7 +8775,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8771,33 +8799,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB72" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -8825,32 +8857,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8858,7 +8894,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -8882,37 +8918,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -8940,32 +8976,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:52</t>
@@ -8973,7 +9013,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -8997,17 +9037,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9017,17 +9057,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -9055,32 +9095,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -9088,7 +9132,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9112,37 +9156,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -9203,7 +9247,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9396,32 +9440,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9429,7 +9477,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9453,37 +9501,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9592,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9598,7 +9646,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -9659,7 +9707,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9713,7 +9761,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9822,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -9823,7 +9871,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -9889,7 +9937,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -9933,17 +9981,477 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>9/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>7/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>6/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr">
-        <is>
-          <t>2/13</t>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>4/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-182路.xlsx
+++ b/data/export/2026-10-29-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -939,12 +939,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1164,22 +1164,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1399,17 +1399,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1509,22 +1509,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1749,12 +1749,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1854,22 +1854,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2200,17 +2200,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2315,12 +2315,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2545,17 +2545,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2655,22 +2655,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2890,17 +2890,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3000,22 +3000,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3345,22 +3345,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3691,17 +3691,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4036,17 +4036,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4146,22 +4146,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4266,17 +4266,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4376,22 +4376,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4606,22 +4606,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5067,17 +5067,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5177,22 +5177,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5292,22 +5292,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5522,22 +5522,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5642,17 +5642,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5983,17 +5983,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6102,17 +6102,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6459,17 +6459,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6931,17 +6931,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7045,22 +7045,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -7125,7 +7125,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7402,22 +7402,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7636,22 +7636,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -7994,17 +7994,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8338,22 +8338,22 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8581,17 +8581,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8695,22 +8695,22 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8814,22 +8814,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -8938,17 +8938,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -9105,24 +9105,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9181,12 +9181,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -9214,32 +9214,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9247,7 +9251,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9271,17 +9275,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9291,17 +9295,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -9450,24 +9454,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9477,7 +9481,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9526,7 +9530,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9559,32 +9563,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9592,7 +9600,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9616,17 +9624,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9636,12 +9644,12 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9674,32 +9682,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9707,7 +9719,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9731,37 +9743,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -9789,32 +9801,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -9822,7 +9838,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -9846,17 +9862,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -9866,17 +9882,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -9904,32 +9920,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -9937,7 +9957,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -9961,37 +9981,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -10019,32 +10039,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10052,7 +10076,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10076,17 +10100,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10096,17 +10120,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -10167,7 +10191,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10216,12 +10240,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -10249,32 +10273,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -10282,7 +10310,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10306,37 +10334,37 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -10397,7 +10425,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10446,12 +10474,357 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
           <t>4/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>1/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-182路.xlsx
+++ b/data/export/2026-10-29-182路.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1744,17 +1744,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2085,17 +2085,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3235,17 +3235,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3576,17 +3576,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4726,17 +4726,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6340,17 +6340,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7169,17 +7169,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7646,12 +7646,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7879,17 +7879,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -8299,7 +8299,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8705,12 +8705,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -8943,12 +8943,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -9067,7 +9067,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -9132,7 +9132,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9176,17 +9176,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9525,17 +9525,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9930,12 +9930,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10006,12 +10006,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -10049,24 +10049,24 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -10158,32 +10158,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -10191,7 +10195,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10215,17 +10219,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10235,17 +10239,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -10283,12 +10287,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
@@ -10310,7 +10314,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10359,12 +10363,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -10392,32 +10396,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10425,7 +10433,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10449,17 +10457,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10469,17 +10477,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -10540,7 +10548,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10655,7 +10663,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10704,12 +10712,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10778,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10819,12 +10827,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
